--- a/Test/record document/13.xlsx
+++ b/Test/record document/13.xlsx
@@ -422,9 +422,15 @@
           <t>Name</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mary Chan</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2025/06</t>
+          <t>2025/07</t>
         </is>
       </c>
     </row>
@@ -434,6 +440,11 @@
           <t>Birth date</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1938/3/8</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -443,11 +454,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13號床</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>Day</t>
@@ -615,6 +627,7 @@
           <t>Month</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1138,11 +1151,6 @@
       <c r="A80" t="inlineStr">
         <is>
           <t>18:30</t>
-        </is>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>✓ 2025/06/29,18:23:24</t>
         </is>
       </c>
     </row>
